--- a/demo.xlsx
+++ b/demo.xlsx
@@ -23,6 +23,7 @@
     <sheet name="11월" sheetId="13" state="visible" r:id="rId15"/>
     <sheet name="12월" sheetId="14" state="visible" r:id="rId16"/>
     <sheet name="설정" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="결산" sheetId="16" state="visible" r:id="rId18"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="152">
   <si>
     <t xml:space="preserve">각 월 시트에서 자동으로 가져옵니다 (입력 불필요)</t>
   </si>
@@ -1710,6 +1711,2108 @@
       <t xml:space="preserve">.</t>
     </r>
   </si>
+  <si>
+    <t xml:space="preserve">연월</t>
+  </si>
+  <si>
+    <t xml:space="preserve">작성일</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제목</t>
+  </si>
+  <si>
+    <t xml:space="preserve">한 줄 요약</t>
+  </si>
+  <si>
+    <t xml:space="preserve">본문</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상태</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-05</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">년 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">월 결산</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">순자산은 808만원 늘어 5억 7,015만원이에요. 주식은 기술주 조정으로 450만원 빠졌지만 상여 덕분에 저축 합계가 575만원으로 올해 최고예요. (예시)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">## 1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한눈에 보기
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">항목 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">월 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전월 대비 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|
+|---|---|---|
+| **</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">순자산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">** | **5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">억 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7,015</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">** | **+808</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(+1.4%)** |
+| </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주식 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">참</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정윤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) | 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">억 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">900</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| −450</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(−4.0%) |
+| </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부동산 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아파트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) | 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">억 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5,500</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| +500</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(+0.8%) |
+| </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저축 합계 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| 575</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| +146</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|
+| </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저축 외 자산 변동 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| +233</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저축 제외 수익률 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.4% |
+## 2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">투자 성과와 시황
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">### </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주식 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">450</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">- **3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">월</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:** (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미국 기술주 조정으로 지수가 내리면서 계좌도 함께 빠졌어요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.
+- **4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">월</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:** (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실적 발표 시즌이라 반등 기대와 금리 부담이 함께 있어요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.
+### </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">퇴직금 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비트코인
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">- (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비트코인은 월말 반등으로 크게 올랐어요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.
+### </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부동산 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+500</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">- **3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">월</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:** (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지역 아파트값이 꾸준히 올랐어요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.
+- **</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전망</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:** (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">새 공급이 적어 크게 하락할 요인은 적어 보여요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.
+## 3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가계부 요약
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수입 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">900</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상여</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기타수입 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">150</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 더해졌어요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지출 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">440</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">월과 비슷해요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">초과금 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원이 새로 생겼어요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저축 합계 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">575</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일반 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">460</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대출상환 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">115</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저축률 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">63.9%)
+## 4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 달 체크포인트
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">- **</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상여 제외 저축률</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:** </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상여를 빼면 일반 저축은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">310</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원으로 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">월과 비슷해요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.
+- **</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">초과금 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:** </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일회성인지 확인해 두면 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">월 변동비를 예측하기 쉬워요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">확정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-05</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">년 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">월 결산</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">지출은 1월과 같았고 저축 합계 429만원(57.2%)이에요. 순자산 +658만원.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">## 1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이번 달 숫자
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">항목 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">월 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">월 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전월 대비 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|
+|---|---|---|---|
+| </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수입 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| 750</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| 760</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| −10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|
+| </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지출 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| 436</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| 437</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| −1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|
+| **</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저축 합계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">** | **429</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">** | 443</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">| −14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|
+## 2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요약
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">생활비가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">165</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원으로 늘었지만 초과금이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원이라 지출은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">월과 같아요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">순자산 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+658</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저축 합계 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">429</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저축 외 변동 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">229</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -1724,7 +3827,7 @@
     <numFmt numFmtId="169" formatCode="0\월;;\-"/>
     <numFmt numFmtId="170" formatCode="0"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1955,6 +4058,26 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2025,7 +4148,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2152,6 +4275,18 @@
     </xf>
     <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2699,8 +4834,8 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="7384368"/>
-        <c:axId val="89275011"/>
+        <c:axId val="18014987"/>
+        <c:axId val="45230986"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2861,11 +4996,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="23553802"/>
-        <c:axId val="86847826"/>
+        <c:axId val="49928134"/>
+        <c:axId val="89098406"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="7384368"/>
+        <c:axId val="18014987"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2897,7 +5032,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89275011"/>
+        <c:crossAx val="45230986"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2905,7 +5040,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="89275011"/>
+        <c:axId val="45230986"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2981,12 +5116,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7384368"/>
+        <c:crossAx val="18014987"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="23553802"/>
+        <c:axId val="49928134"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3018,7 +5153,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86847826"/>
+        <c:crossAx val="89098406"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3026,7 +5161,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="86847826"/>
+        <c:axId val="89098406"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3092,7 +5227,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23553802"/>
+        <c:crossAx val="49928134"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6005,11 +8140,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="24812510"/>
-        <c:axId val="60738256"/>
+        <c:axId val="38766835"/>
+        <c:axId val="36900337"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="24812510"/>
+        <c:axId val="38766835"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6041,7 +8176,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60738256"/>
+        <c:crossAx val="36900337"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6049,7 +8184,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="60738256"/>
+        <c:axId val="36900337"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6091,7 +8226,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24812510"/>
+        <c:crossAx val="38766835"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9169,11 +11304,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="72127129"/>
-        <c:axId val="11575719"/>
+        <c:axId val="87571929"/>
+        <c:axId val="31440543"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="72127129"/>
+        <c:axId val="87571929"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9205,7 +11340,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11575719"/>
+        <c:crossAx val="31440543"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9213,7 +11348,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11575719"/>
+        <c:axId val="31440543"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9255,7 +11390,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72127129"/>
+        <c:crossAx val="87571929"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9852,11 +11987,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="7612099"/>
-        <c:axId val="17539117"/>
+        <c:axId val="1169317"/>
+        <c:axId val="69066528"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="7612099"/>
+        <c:axId val="1169317"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9888,7 +12023,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17539117"/>
+        <c:crossAx val="69066528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9896,7 +12031,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="17539117"/>
+        <c:axId val="69066528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9938,7 +12073,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7612099"/>
+        <c:crossAx val="1169317"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10867,11 +13002,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="84007785"/>
-        <c:axId val="50378569"/>
+        <c:axId val="84377969"/>
+        <c:axId val="37386782"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="84007785"/>
+        <c:axId val="84377969"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10903,7 +13038,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50378569"/>
+        <c:crossAx val="37386782"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10911,7 +13046,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50378569"/>
+        <c:axId val="37386782"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10953,7 +13088,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84007785"/>
+        <c:crossAx val="84377969"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12028,9 +14163,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>581040</xdr:colOff>
+      <xdr:colOff>579960</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>79200</xdr:rowOff>
+      <xdr:rowOff>78120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12039,7 +14174,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="12312000" y="563760"/>
-        <a:ext cx="7919280" cy="3239640"/>
+        <a:ext cx="7918200" cy="3238560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12058,9 +14193,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>581040</xdr:colOff>
+      <xdr:colOff>579960</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>78840</xdr:rowOff>
+      <xdr:rowOff>77760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12069,7 +14204,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="12312000" y="4183560"/>
-        <a:ext cx="7919280" cy="3238920"/>
+        <a:ext cx="7918200" cy="3237840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12088,9 +14223,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>581040</xdr:colOff>
+      <xdr:colOff>579960</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>78840</xdr:rowOff>
+      <xdr:rowOff>77760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12099,7 +14234,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="12312000" y="7803000"/>
-        <a:ext cx="7919280" cy="3239280"/>
+        <a:ext cx="7918200" cy="3238200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12123,9 +14258,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>100080</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12134,7 +14269,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="563760"/>
-        <a:ext cx="3959280" cy="2879640"/>
+        <a:ext cx="3958200" cy="2878560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12153,9 +14288,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>99720</xdr:rowOff>
+      <xdr:rowOff>98640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12164,7 +14299,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="3802320"/>
-        <a:ext cx="3959280" cy="2879280"/>
+        <a:ext cx="3958200" cy="2878200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12188,9 +14323,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>100080</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12199,7 +14334,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="563760"/>
-        <a:ext cx="3959280" cy="2879640"/>
+        <a:ext cx="3958200" cy="2878560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12218,9 +14353,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>99720</xdr:rowOff>
+      <xdr:rowOff>98640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12229,7 +14364,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="3802320"/>
-        <a:ext cx="3959280" cy="2879280"/>
+        <a:ext cx="3958200" cy="2878200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12253,9 +14388,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>100080</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12264,7 +14399,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="563760"/>
-        <a:ext cx="3959280" cy="2879640"/>
+        <a:ext cx="3958200" cy="2878560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12283,9 +14418,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>99720</xdr:rowOff>
+      <xdr:rowOff>98640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12294,7 +14429,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="3802320"/>
-        <a:ext cx="3959280" cy="2879280"/>
+        <a:ext cx="3958200" cy="2878200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12318,9 +14453,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>100080</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12329,7 +14464,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="563760"/>
-        <a:ext cx="3959280" cy="2879640"/>
+        <a:ext cx="3958200" cy="2878560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12348,9 +14483,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>99720</xdr:rowOff>
+      <xdr:rowOff>98640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12359,7 +14494,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="3802320"/>
-        <a:ext cx="3959280" cy="2879280"/>
+        <a:ext cx="3958200" cy="2878200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12383,9 +14518,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>100080</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12394,7 +14529,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="563760"/>
-        <a:ext cx="3959280" cy="2879640"/>
+        <a:ext cx="3958200" cy="2878560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12413,9 +14548,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>99720</xdr:rowOff>
+      <xdr:rowOff>98640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12424,7 +14559,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="3802320"/>
-        <a:ext cx="3959280" cy="2879280"/>
+        <a:ext cx="3958200" cy="2878200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12448,9 +14583,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
-      <xdr:colOff>472680</xdr:colOff>
+      <xdr:colOff>471600</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>23040</xdr:rowOff>
+      <xdr:rowOff>21960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12459,7 +14594,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="15977160" y="1317600"/>
-        <a:ext cx="7199280" cy="3239280"/>
+        <a:ext cx="7198200" cy="3238200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12478,9 +14613,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
-      <xdr:colOff>472680</xdr:colOff>
+      <xdr:colOff>471600</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>23040</xdr:rowOff>
+      <xdr:rowOff>21960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12489,7 +14624,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="15977160" y="5127840"/>
-        <a:ext cx="7199280" cy="3239280"/>
+        <a:ext cx="7198200" cy="3238200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12513,9 +14648,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>100080</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12524,7 +14659,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="563760"/>
-        <a:ext cx="3959280" cy="2879640"/>
+        <a:ext cx="3958200" cy="2878560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12543,9 +14678,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>99720</xdr:rowOff>
+      <xdr:rowOff>98640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12554,7 +14689,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="3802320"/>
-        <a:ext cx="3959280" cy="2879280"/>
+        <a:ext cx="3958200" cy="2878200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12578,9 +14713,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>100080</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12589,7 +14724,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="563760"/>
-        <a:ext cx="3959280" cy="2879640"/>
+        <a:ext cx="3958200" cy="2878560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12608,9 +14743,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>99720</xdr:rowOff>
+      <xdr:rowOff>98640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12619,7 +14754,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="3802320"/>
-        <a:ext cx="3959280" cy="2879280"/>
+        <a:ext cx="3958200" cy="2878200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12643,9 +14778,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>100080</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12654,7 +14789,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="563760"/>
-        <a:ext cx="3959280" cy="2879640"/>
+        <a:ext cx="3958200" cy="2878560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12673,9 +14808,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>99720</xdr:rowOff>
+      <xdr:rowOff>98640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12684,7 +14819,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="3802320"/>
-        <a:ext cx="3959280" cy="2879280"/>
+        <a:ext cx="3958200" cy="2878200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12708,9 +14843,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>100080</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12719,7 +14854,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="563760"/>
-        <a:ext cx="3959280" cy="2879640"/>
+        <a:ext cx="3958200" cy="2878560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12738,9 +14873,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>99720</xdr:rowOff>
+      <xdr:rowOff>98640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12749,7 +14884,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="3802320"/>
-        <a:ext cx="3959280" cy="2879280"/>
+        <a:ext cx="3958200" cy="2878200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12773,9 +14908,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>100080</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12784,7 +14919,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="563760"/>
-        <a:ext cx="3959280" cy="2879640"/>
+        <a:ext cx="3958200" cy="2878560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12803,9 +14938,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>99720</xdr:rowOff>
+      <xdr:rowOff>98640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12814,7 +14949,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="3802320"/>
-        <a:ext cx="3959280" cy="2879280"/>
+        <a:ext cx="3958200" cy="2878200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12838,9 +14973,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>100080</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12849,7 +14984,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="563760"/>
-        <a:ext cx="3959280" cy="2879640"/>
+        <a:ext cx="3958200" cy="2878560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12868,9 +15003,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>99720</xdr:rowOff>
+      <xdr:rowOff>98640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12879,7 +15014,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="3802320"/>
-        <a:ext cx="3959280" cy="2879280"/>
+        <a:ext cx="3958200" cy="2878200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12903,9 +15038,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>100080</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12914,7 +15049,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="563760"/>
-        <a:ext cx="3959280" cy="2879640"/>
+        <a:ext cx="3958200" cy="2878560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12933,9 +15068,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>99720</xdr:rowOff>
+      <xdr:rowOff>98640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12944,7 +15079,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6273000" y="3802320"/>
-        <a:ext cx="3959280" cy="2879280"/>
+        <a:ext cx="3958200" cy="2878200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -15912,6 +18047,93 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" s="32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="495.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
